--- a/dialogue_lines.xlsx
+++ b/dialogue_lines.xlsx
@@ -4065,7 +4065,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Make a fuss of him</t>
+          <t>Hype him up about it</t>
         </is>
       </c>
     </row>

--- a/dialogue_lines.xlsx
+++ b/dialogue_lines.xlsx
@@ -665,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -707,6 +708,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
@@ -738,7 +740,9 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            transfer, dreammove, ambition, injury. kind 'any' reply rows are shared by all kinds.</t>
+          <t xml:space="preserve">            transfer, dreammove, ambition, injury, injuryagain (3rd+ long layoff), intlcallup,
+            intldebut, intlfirstgoal, firsttrophy, intltrophy (+ ...grp variants that name
+            the other clients who won it: {others}, {trophy}, {nation}). kind 'any' reply rows are shared by all kinds.</t>
         </is>
       </c>
     </row>
@@ -749,6 +753,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
@@ -5878,7 +5883,6 @@
           <t>titlemiss-open</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>any</t>
@@ -5906,7 +5910,6 @@
           <t>titlemiss-open</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>any</t>
@@ -5934,7 +5937,6 @@
           <t>titlemiss-open</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>any</t>
@@ -7801,7 +7803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9145,13 +9147,625 @@
       </c>
     </row>
     <row r="47">
-      <c r="F47" s="2" t="n"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>M046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>injury</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>{weeks} weeks on the sidelines. I just lie here staring at the ceiling, {agent}.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="F48" s="2" t="n"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>M047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>injury</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>The doctor said {weeks} weeks. I heard the number and stopped listening.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="F49" s="2" t="n"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>M048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>injury</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>humble</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>{weeks} weeks out. Sorry, {agent}. I know the timing is terrible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>injuryagain</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Not again, {agent}. Another {weeks} weeks. I'm starting to think my body hates me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>M050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>injuryagain</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Why always me? {weeks} more weeks out. I really can't take this anymore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>injuryagain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>hothead</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AGAIN?! {weeks} weeks! I swear, I can't go through another one of these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>M052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>injuryagain</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Another long one. {weeks} weeks. I'll do the rehab like always, but I'm tired of starting over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>M053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>intlcallup</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>I'm in the {nation} squad, {agent}! My phone hasn't stopped buzzing. My mum cried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>M054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>intlcallup</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>humble</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>They called me up for {nation}. Me! I read the list three times to be sure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>M055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>intlcallup</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>showman</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>National team, {agent}! {nation} finally noticed. About time, if you ask me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>M056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>intldebut</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>I played for {nation}, {agent}! The anthem, the shirt, all of it. Goosebumps the whole match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>M057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>intldebut</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>loyal</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>My first cap for {nation}. I thought about everyone who got me here. You're on that list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>M058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>intlfirstgoal</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>I scored for {nation}! I don't think I've stopped smiling since the final whistle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>M059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>intlfirstgoal</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>showman</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>First goal for {nation}. They'll be singing my name back home tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>M060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>firsttrophy</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>My first trophy, {agent}! {trophy}! I'm holding the medal right now. It's heavier than it looks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>M061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>firsttrophy</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>humble</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>I've actually won something. {trophy}. I keep checking the medal to make sure it's real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>M062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>firsttrophy</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>showman</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>{trophy} winner! The first of many, {agent}. Start clearing some shelf space.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>M063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>firsttrophygrp</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>We won it, {agent}! {trophy}! {others} and I are just so ecstatic. My first ever trophy!</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>M064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>firsttrophygrp</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>{others} and I have been dancing in the dressing room for an hour. {trophy}! My very first!</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>M065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>intltrophy</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>We won {trophy} with {nation}, {agent}! The whole country is out in the streets!</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>M066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>intltrophy</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>loyal</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>{trophy} with {nation}. For my family, for everyone back home. And for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>M067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>intltrophygrp</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>{trophy}! {others} and I are just so ecstatic. {nation} will never forget this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>M068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>intltrophygrp</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>showman</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>{nation} won {trophy}, and {others} and I were right in the middle of it. Tonight we party.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
